--- a/results/breakdown/2020/nitrous oxide production, AON 88, fossil ammonia.xlsx
+++ b/results/breakdown/2020/nitrous oxide production, AON 88, fossil ammonia.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="11">
   <si>
     <t>target</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>'market for wastewater, average' (cubic meter, RoW, None)</t>
+  </si>
+  <si>
+    <t>'market for gold' (kilogram, GLO, None)</t>
   </si>
   <si>
     <t>'market group for electricity, high voltage' (kilowatt hour, GLO, None)</t>
@@ -401,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -420,7 +423,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
@@ -429,7 +432,7 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>4.174313561971488</v>
+        <v>4.17887398187466</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -446,7 +449,7 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>3.12927338797176</v>
+        <v>3.129273387971764</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -463,7 +466,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>0.0006465902749788597</v>
+        <v>0.000646590274978857</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -480,7 +483,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>0.04123567392694851</v>
+        <v>0.004560419875350135</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -497,7 +500,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>0.001750823457095508</v>
+        <v>0.04123567392694848</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -514,9 +517,26 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>0.9467451327776356</v>
+        <v>0.001750823457095507</v>
       </c>
       <c r="E7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8">
+        <v>0.9467451327776366</v>
+      </c>
+      <c r="E8">
         <v>1</v>
       </c>
     </row>
